--- a/research/traditional_assets/database/data/germany/germany_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00375</v>
+        <v>-0.0526</v>
       </c>
       <c r="E2">
-        <v>0.0193</v>
+        <v>0.00593</v>
       </c>
       <c r="G2">
-        <v>0.1218009374381093</v>
+        <v>0.2040068709247704</v>
       </c>
       <c r="H2">
-        <v>0.1218009374381093</v>
+        <v>0.2040068709247704</v>
       </c>
       <c r="I2">
-        <v>0.1130647184384834</v>
+        <v>0.1258150459230176</v>
       </c>
       <c r="J2">
-        <v>0.08134279900198098</v>
+        <v>0.1015316519384734</v>
       </c>
       <c r="K2">
-        <v>319.4</v>
+        <v>271.2</v>
       </c>
       <c r="L2">
-        <v>0.03514292630328103</v>
+        <v>0.04753558157470378</v>
       </c>
       <c r="M2">
-        <v>70.5561</v>
+        <v>59.6869</v>
       </c>
       <c r="N2">
-        <v>0.03767010144153764</v>
+        <v>0.03861730072463768</v>
       </c>
       <c r="O2">
-        <v>0.2209020037570445</v>
+        <v>0.2200844395280236</v>
       </c>
       <c r="P2">
-        <v>70.5561</v>
+        <v>59.6869</v>
       </c>
       <c r="Q2">
-        <v>0.03767010144153764</v>
+        <v>0.03861730072463768</v>
       </c>
       <c r="R2">
-        <v>0.2209020037570445</v>
+        <v>0.2200844395280236</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>53.1</v>
+        <v>86.7</v>
       </c>
       <c r="V2">
-        <v>0.02835024025627336</v>
+        <v>0.05609472049689442</v>
       </c>
       <c r="W2">
-        <v>0.0542044972422571</v>
+        <v>0.04846838474461165</v>
       </c>
       <c r="X2">
-        <v>0.1282572431800917</v>
+        <v>0.1977606530769712</v>
       </c>
       <c r="Y2">
-        <v>-0.07405274593783462</v>
+        <v>-0.1492922683323596</v>
       </c>
       <c r="Z2">
-        <v>0.8560018836825996</v>
+        <v>0.5455606024384414</v>
       </c>
       <c r="AA2">
-        <v>0.06962958916971079</v>
+        <v>0.0553916691981237</v>
       </c>
       <c r="AB2">
-        <v>0.04722185346075559</v>
+        <v>0.07091270791244175</v>
       </c>
       <c r="AC2">
-        <v>0.0224077357089552</v>
+        <v>-0.01552103871431805</v>
       </c>
       <c r="AD2">
-        <v>4915.2</v>
+        <v>5186.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4915.2</v>
+        <v>5186.3</v>
       </c>
       <c r="AG2">
-        <v>4862.099999999999</v>
+        <v>5099.6</v>
       </c>
       <c r="AH2">
-        <v>0.7240800212132819</v>
+        <v>0.7704065716959552</v>
       </c>
       <c r="AI2">
-        <v>0.4660061625977719</v>
+        <v>0.5955103915489723</v>
       </c>
       <c r="AJ2">
-        <v>0.7219046487802705</v>
+        <v>0.7674110636248721</v>
       </c>
       <c r="AK2">
-        <v>0.4633042384509833</v>
+        <v>0.5914431184254783</v>
       </c>
       <c r="AL2">
-        <v>526.9</v>
+        <v>370.7</v>
       </c>
       <c r="AM2">
-        <v>526.9</v>
+        <v>370.7</v>
       </c>
       <c r="AN2">
-        <v>4.354358610914245</v>
+        <v>6.323984879892696</v>
       </c>
       <c r="AO2">
-        <v>1.950275194534067</v>
+        <v>1.936336660372269</v>
       </c>
       <c r="AP2">
-        <v>4.307317505315379</v>
+        <v>6.218266065114011</v>
       </c>
       <c r="AQ2">
-        <v>1.950275194534067</v>
+        <v>1.936336660372269</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00375</v>
+        <v>-0.0526</v>
       </c>
       <c r="E3">
-        <v>0.0193</v>
+        <v>0.00593</v>
       </c>
       <c r="G3">
-        <v>0.1218009374381093</v>
+        <v>0.2040068709247704</v>
       </c>
       <c r="H3">
-        <v>0.1218009374381093</v>
+        <v>0.2040068709247704</v>
       </c>
       <c r="I3">
-        <v>0.1130647184384834</v>
+        <v>0.1258150459230176</v>
       </c>
       <c r="J3">
-        <v>0.08134279900198098</v>
+        <v>0.1015316519384734</v>
       </c>
       <c r="K3">
-        <v>319.4</v>
+        <v>271.2</v>
       </c>
       <c r="L3">
-        <v>0.03514292630328103</v>
+        <v>0.04753558157470378</v>
       </c>
       <c r="M3">
-        <v>70.5561</v>
+        <v>59.6869</v>
       </c>
       <c r="N3">
-        <v>0.03767010144153764</v>
+        <v>0.03861730072463768</v>
       </c>
       <c r="O3">
-        <v>0.2209020037570445</v>
+        <v>0.2200844395280236</v>
       </c>
       <c r="P3">
-        <v>70.5561</v>
+        <v>59.6869</v>
       </c>
       <c r="Q3">
-        <v>0.03767010144153764</v>
+        <v>0.03861730072463768</v>
       </c>
       <c r="R3">
-        <v>0.2209020037570445</v>
+        <v>0.2200844395280236</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>53.1</v>
+        <v>86.7</v>
       </c>
       <c r="V3">
-        <v>0.02835024025627336</v>
+        <v>0.05609472049689442</v>
       </c>
       <c r="W3">
-        <v>0.0542044972422571</v>
+        <v>0.04846838474461165</v>
       </c>
       <c r="X3">
-        <v>0.1282572431800917</v>
+        <v>0.1977606530769712</v>
       </c>
       <c r="Y3">
-        <v>-0.07405274593783462</v>
+        <v>-0.1492922683323596</v>
       </c>
       <c r="Z3">
-        <v>0.8560018836825996</v>
+        <v>0.5455606024384414</v>
       </c>
       <c r="AA3">
-        <v>0.06962958916971079</v>
+        <v>0.0553916691981237</v>
       </c>
       <c r="AB3">
-        <v>0.04722185346075559</v>
+        <v>0.07091270791244175</v>
       </c>
       <c r="AC3">
-        <v>0.0224077357089552</v>
+        <v>-0.01552103871431805</v>
       </c>
       <c r="AD3">
-        <v>4915.2</v>
+        <v>5186.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4915.2</v>
+        <v>5186.3</v>
       </c>
       <c r="AG3">
-        <v>4862.099999999999</v>
+        <v>5099.6</v>
       </c>
       <c r="AH3">
-        <v>0.7240800212132819</v>
+        <v>0.7704065716959552</v>
       </c>
       <c r="AI3">
-        <v>0.4660061625977719</v>
+        <v>0.5955103915489723</v>
       </c>
       <c r="AJ3">
-        <v>0.7219046487802705</v>
+        <v>0.7674110636248721</v>
       </c>
       <c r="AK3">
-        <v>0.4633042384509833</v>
+        <v>0.5914431184254783</v>
       </c>
       <c r="AL3">
-        <v>526.9</v>
+        <v>370.7</v>
       </c>
       <c r="AM3">
-        <v>526.9</v>
+        <v>370.7</v>
       </c>
       <c r="AN3">
-        <v>4.354358610914245</v>
+        <v>6.323984879892696</v>
       </c>
       <c r="AO3">
-        <v>1.950275194534067</v>
+        <v>1.936336660372269</v>
       </c>
       <c r="AP3">
-        <v>4.307317505315379</v>
+        <v>6.218266065114011</v>
       </c>
       <c r="AQ3">
-        <v>1.950275194534067</v>
+        <v>1.936336660372269</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0526</v>
+        <v>-0.0299</v>
       </c>
       <c r="E2">
-        <v>0.00593</v>
+        <v>-0.0337</v>
       </c>
       <c r="G2">
-        <v>0.2040068709247704</v>
+        <v>0.1257782264849403</v>
       </c>
       <c r="H2">
-        <v>0.2040068709247704</v>
+        <v>0.1257782264849403</v>
       </c>
       <c r="I2">
-        <v>0.1258150459230176</v>
+        <v>0.09956251051657412</v>
       </c>
       <c r="J2">
-        <v>0.1015316519384734</v>
+        <v>0.06948558772894287</v>
       </c>
       <c r="K2">
-        <v>271.2</v>
+        <v>191.5</v>
       </c>
       <c r="L2">
-        <v>0.04753558157470378</v>
+        <v>0.03222278310617533</v>
       </c>
       <c r="M2">
-        <v>59.6869</v>
+        <v>64.46559999999999</v>
       </c>
       <c r="N2">
-        <v>0.03861730072463768</v>
+        <v>0.0466601042269832</v>
       </c>
       <c r="O2">
-        <v>0.2200844395280236</v>
+        <v>0.3366349869451697</v>
       </c>
       <c r="P2">
-        <v>59.6869</v>
+        <v>64.46559999999999</v>
       </c>
       <c r="Q2">
-        <v>0.03861730072463768</v>
+        <v>0.0466601042269832</v>
       </c>
       <c r="R2">
-        <v>0.2200844395280236</v>
+        <v>0.3366349869451697</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>86.7</v>
+        <v>52.6</v>
       </c>
       <c r="V2">
-        <v>0.05609472049689442</v>
+        <v>0.03807180081065432</v>
       </c>
       <c r="W2">
-        <v>0.04846838474461165</v>
+        <v>0.05423853626759566</v>
       </c>
       <c r="X2">
-        <v>0.1977606530769712</v>
+        <v>0.1715418910103507</v>
       </c>
       <c r="Y2">
-        <v>-0.1492922683323596</v>
+        <v>-0.1173033547427551</v>
       </c>
       <c r="Z2">
-        <v>0.5455606024384414</v>
+        <v>0.6886203260605078</v>
       </c>
       <c r="AA2">
-        <v>0.0553916691981237</v>
+        <v>0.04784918807841065</v>
       </c>
       <c r="AB2">
-        <v>0.07091270791244175</v>
+        <v>0.0602965942315266</v>
       </c>
       <c r="AC2">
-        <v>-0.01552103871431805</v>
+        <v>-0.01244740615311594</v>
       </c>
       <c r="AD2">
-        <v>5186.3</v>
+        <v>5342.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5186.3</v>
+        <v>5342.9</v>
       </c>
       <c r="AG2">
-        <v>5099.6</v>
+        <v>5290.299999999999</v>
       </c>
       <c r="AH2">
-        <v>0.7704065716959552</v>
+        <v>0.7945423451557736</v>
       </c>
       <c r="AI2">
-        <v>0.5955103915489723</v>
+        <v>0.5122676152216225</v>
       </c>
       <c r="AJ2">
-        <v>0.7674110636248721</v>
+        <v>0.7929225557937019</v>
       </c>
       <c r="AK2">
-        <v>0.5914431184254783</v>
+        <v>0.5097954188469062</v>
       </c>
       <c r="AL2">
-        <v>370.7</v>
+        <v>433.2</v>
       </c>
       <c r="AM2">
-        <v>370.7</v>
+        <v>433.2</v>
       </c>
       <c r="AN2">
-        <v>6.323984879892696</v>
+        <v>7.655681329703396</v>
       </c>
       <c r="AO2">
-        <v>1.936336660372269</v>
+        <v>1.365881809787627</v>
       </c>
       <c r="AP2">
-        <v>6.218266065114011</v>
+        <v>7.580312365668433</v>
       </c>
       <c r="AQ2">
-        <v>1.936336660372269</v>
+        <v>1.365881809787627</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0526</v>
+        <v>-0.0299</v>
       </c>
       <c r="E3">
-        <v>0.00593</v>
+        <v>-0.0337</v>
       </c>
       <c r="G3">
-        <v>0.2040068709247704</v>
+        <v>0.1257782264849403</v>
       </c>
       <c r="H3">
-        <v>0.2040068709247704</v>
+        <v>0.1257782264849403</v>
       </c>
       <c r="I3">
-        <v>0.1258150459230176</v>
+        <v>0.09956251051657412</v>
       </c>
       <c r="J3">
-        <v>0.1015316519384734</v>
+        <v>0.06948558772894287</v>
       </c>
       <c r="K3">
-        <v>271.2</v>
+        <v>191.5</v>
       </c>
       <c r="L3">
-        <v>0.04753558157470378</v>
+        <v>0.03222278310617533</v>
       </c>
       <c r="M3">
-        <v>59.6869</v>
+        <v>64.46559999999999</v>
       </c>
       <c r="N3">
-        <v>0.03861730072463768</v>
+        <v>0.0466601042269832</v>
       </c>
       <c r="O3">
-        <v>0.2200844395280236</v>
+        <v>0.3366349869451697</v>
       </c>
       <c r="P3">
-        <v>59.6869</v>
+        <v>64.46559999999999</v>
       </c>
       <c r="Q3">
-        <v>0.03861730072463768</v>
+        <v>0.0466601042269832</v>
       </c>
       <c r="R3">
-        <v>0.2200844395280236</v>
+        <v>0.3366349869451697</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>86.7</v>
+        <v>52.6</v>
       </c>
       <c r="V3">
-        <v>0.05609472049689442</v>
+        <v>0.03807180081065432</v>
       </c>
       <c r="W3">
-        <v>0.04846838474461165</v>
+        <v>0.05423853626759566</v>
       </c>
       <c r="X3">
-        <v>0.1977606530769712</v>
+        <v>0.1715418910103507</v>
       </c>
       <c r="Y3">
-        <v>-0.1492922683323596</v>
+        <v>-0.1173033547427551</v>
       </c>
       <c r="Z3">
-        <v>0.5455606024384414</v>
+        <v>0.6886203260605078</v>
       </c>
       <c r="AA3">
-        <v>0.0553916691981237</v>
+        <v>0.04784918807841065</v>
       </c>
       <c r="AB3">
-        <v>0.07091270791244175</v>
+        <v>0.0602965942315266</v>
       </c>
       <c r="AC3">
-        <v>-0.01552103871431805</v>
+        <v>-0.01244740615311594</v>
       </c>
       <c r="AD3">
-        <v>5186.3</v>
+        <v>5342.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5186.3</v>
+        <v>5342.9</v>
       </c>
       <c r="AG3">
-        <v>5099.6</v>
+        <v>5290.299999999999</v>
       </c>
       <c r="AH3">
-        <v>0.7704065716959552</v>
+        <v>0.7945423451557736</v>
       </c>
       <c r="AI3">
-        <v>0.5955103915489723</v>
+        <v>0.5122676152216225</v>
       </c>
       <c r="AJ3">
-        <v>0.7674110636248721</v>
+        <v>0.7929225557937019</v>
       </c>
       <c r="AK3">
-        <v>0.5914431184254783</v>
+        <v>0.5097954188469062</v>
       </c>
       <c r="AL3">
-        <v>370.7</v>
+        <v>433.2</v>
       </c>
       <c r="AM3">
-        <v>370.7</v>
+        <v>433.2</v>
       </c>
       <c r="AN3">
-        <v>6.323984879892696</v>
+        <v>7.655681329703396</v>
       </c>
       <c r="AO3">
-        <v>1.936336660372269</v>
+        <v>1.365881809787627</v>
       </c>
       <c r="AP3">
-        <v>6.218266065114011</v>
+        <v>7.580312365668433</v>
       </c>
       <c r="AQ3">
-        <v>1.936336660372269</v>
+        <v>1.365881809787627</v>
       </c>
     </row>
   </sheetData>
